--- a/AAII_Financials/Quarterly/AONC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AONC_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>

--- a/AAII_Financials/Quarterly/AONC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AONC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="92">
   <si>
     <t>AONC</t>
   </si>
@@ -656,148 +656,186 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>4</v>
+      <c r="D8" s="3">
+        <v>364300</v>
       </c>
       <c r="E8" s="3">
-        <v>0</v>
+        <v>324200</v>
       </c>
       <c r="F8" s="3">
-        <v>0</v>
+        <v>336300</v>
       </c>
       <c r="G8" s="3">
-        <v>0</v>
+        <v>618700</v>
       </c>
       <c r="H8" s="3">
-        <v>0</v>
+        <v>303700</v>
       </c>
       <c r="I8" s="3">
-        <v>0</v>
+        <v>300400</v>
       </c>
       <c r="J8" s="3">
-        <v>0</v>
+        <v>297300</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>4</v>
+      <c r="D9" s="3">
+        <v>354900</v>
+      </c>
+      <c r="E9" s="3">
+        <v>315600</v>
+      </c>
+      <c r="F9" s="3">
+        <v>310900</v>
+      </c>
+      <c r="G9" s="3">
+        <v>569900</v>
+      </c>
+      <c r="H9" s="3">
+        <v>278500</v>
+      </c>
+      <c r="I9" s="3">
+        <v>273600</v>
+      </c>
+      <c r="J9" s="3">
+        <v>267600</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>4</v>
+      <c r="D10" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E10" s="3">
+        <v>8600</v>
+      </c>
+      <c r="F10" s="3">
+        <v>25400</v>
+      </c>
+      <c r="G10" s="3">
+        <v>48800</v>
+      </c>
+      <c r="H10" s="3">
+        <v>25200</v>
+      </c>
+      <c r="I10" s="3">
+        <v>26800</v>
+      </c>
+      <c r="J10" s="3">
+        <v>29700</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -809,8 +847,11 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -838,8 +879,17 @@
       <c r="K12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -867,37 +917,55 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>24600</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
+        <v>5300</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -925,8 +993,17 @@
       <c r="K15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -935,66 +1012,87 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1500</v>
+        <v>383600</v>
       </c>
       <c r="E17" s="3">
-        <v>1000</v>
+        <v>344800</v>
       </c>
       <c r="F17" s="3">
+        <v>360700</v>
+      </c>
+      <c r="G17" s="3">
+        <v>622800</v>
+      </c>
+      <c r="H17" s="3">
+        <v>304200</v>
+      </c>
+      <c r="I17" s="3">
+        <v>297100</v>
+      </c>
+      <c r="J17" s="3">
+        <v>291200</v>
+      </c>
+      <c r="K17" s="3">
+        <v>300</v>
+      </c>
+      <c r="L17" s="3">
+        <v>300</v>
+      </c>
+      <c r="M17" s="3">
         <v>900</v>
       </c>
-      <c r="G17" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H17" s="3">
-        <v>300</v>
-      </c>
-      <c r="I17" s="3">
-        <v>300</v>
-      </c>
-      <c r="J17" s="3">
-        <v>900</v>
-      </c>
-      <c r="K17" s="3">
+      <c r="N17" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>4</v>
+      <c r="D18" s="3">
+        <v>-19300</v>
       </c>
       <c r="E18" s="3">
-        <v>-1000</v>
+        <v>-20600</v>
       </c>
       <c r="F18" s="3">
+        <v>-24400</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I18" s="3">
+        <v>3300</v>
+      </c>
+      <c r="J18" s="3">
+        <v>6100</v>
+      </c>
+      <c r="K18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M18" s="3">
         <v>-900</v>
       </c>
-      <c r="G18" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-300</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-300</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-900</v>
-      </c>
-      <c r="K18" s="3">
+      <c r="N18" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1006,153 +1104,201 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>4</v>
+      <c r="D20" s="3">
+        <v>-1100</v>
       </c>
       <c r="E20" s="3">
-        <v>1600</v>
+        <v>200</v>
       </c>
       <c r="F20" s="3">
-        <v>3300</v>
+        <v>-2900</v>
       </c>
       <c r="G20" s="3">
-        <v>4700</v>
+        <v>-4300</v>
       </c>
       <c r="H20" s="3">
+        <v>600</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="J20" s="3">
+        <v>500</v>
+      </c>
+      <c r="K20" s="3">
         <v>2200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="L20" s="3">
         <v>3800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="M20" s="3">
         <v>400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="N20" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>4</v>
+      <c r="D21" s="3">
+        <v>-17800</v>
       </c>
       <c r="E21" s="3">
-        <v>600</v>
+        <v>-18300</v>
       </c>
       <c r="F21" s="3">
-        <v>2400</v>
+        <v>-25300</v>
       </c>
       <c r="G21" s="3">
-        <v>3800</v>
+        <v>-4100</v>
       </c>
       <c r="H21" s="3">
+        <v>2200</v>
+      </c>
+      <c r="I21" s="3">
+        <v>4100</v>
+      </c>
+      <c r="J21" s="3">
+        <v>8700</v>
+      </c>
+      <c r="K21" s="3">
         <v>1900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="L21" s="3">
         <v>3500</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-1700</v>
+        <v>-22100</v>
       </c>
       <c r="E23" s="3">
-        <v>600</v>
+        <v>-22300</v>
       </c>
       <c r="F23" s="3">
-        <v>2400</v>
+        <v>-28900</v>
       </c>
       <c r="G23" s="3">
-        <v>3800</v>
+        <v>-11400</v>
       </c>
       <c r="H23" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="I23" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J23" s="3">
+        <v>5600</v>
+      </c>
+      <c r="K23" s="3">
         <v>1900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="L23" s="3">
         <v>3500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="M23" s="3">
         <v>-600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="N23" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="E24" s="3">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="F24" s="3">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="G24" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="H24" s="3">
         <v>0</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1180,66 +1326,93 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-1700</v>
+        <v>-25000</v>
       </c>
       <c r="E26" s="3">
-        <v>200</v>
+        <v>-22300</v>
       </c>
       <c r="F26" s="3">
-        <v>1700</v>
+        <v>-29200</v>
       </c>
       <c r="G26" s="3">
-        <v>3400</v>
+        <v>-11400</v>
       </c>
       <c r="H26" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="I26" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J26" s="3">
+        <v>5600</v>
+      </c>
+      <c r="K26" s="3">
         <v>1900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="L26" s="3">
         <v>3500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="M26" s="3">
         <v>-600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="N26" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-1700</v>
+        <v>-7800</v>
       </c>
       <c r="E27" s="3">
-        <v>200</v>
+        <v>-5100</v>
       </c>
       <c r="F27" s="3">
-        <v>1700</v>
+        <v>-4000</v>
       </c>
       <c r="G27" s="3">
-        <v>3400</v>
+        <v>0</v>
       </c>
       <c r="H27" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="I27" s="3">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3">
+        <v>0</v>
+      </c>
+      <c r="K27" s="3">
         <v>1900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="L27" s="3">
         <v>3500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="M27" s="3">
         <v>-600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="N27" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1267,8 +1440,17 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1296,8 +1478,17 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1325,8 +1516,17 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1354,66 +1554,93 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>4</v>
+      <c r="D32" s="3">
+        <v>1100</v>
       </c>
       <c r="E32" s="3">
-        <v>-1600</v>
+        <v>-200</v>
       </c>
       <c r="F32" s="3">
-        <v>-3300</v>
+        <v>2900</v>
       </c>
       <c r="G32" s="3">
-        <v>-4700</v>
+        <v>4300</v>
       </c>
       <c r="H32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I32" s="3">
+        <v>500</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="K32" s="3">
         <v>-2200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="L32" s="3">
         <v>-3800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="M32" s="3">
         <v>-400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="N32" s="3">
         <v>-3700</v>
       </c>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-1700</v>
+        <v>-7800</v>
       </c>
       <c r="E33" s="3">
-        <v>200</v>
+        <v>-5100</v>
       </c>
       <c r="F33" s="3">
-        <v>1700</v>
+        <v>-4000</v>
       </c>
       <c r="G33" s="3">
-        <v>3400</v>
+        <v>0</v>
       </c>
       <c r="H33" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="I33" s="3">
+        <v>0</v>
+      </c>
+      <c r="J33" s="3">
+        <v>0</v>
+      </c>
+      <c r="K33" s="3">
         <v>1900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="L33" s="3">
         <v>3500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="M33" s="3">
         <v>-600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="N33" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1441,71 +1668,98 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-1700</v>
+        <v>-7800</v>
       </c>
       <c r="E35" s="3">
-        <v>200</v>
+        <v>-5100</v>
       </c>
       <c r="F35" s="3">
-        <v>1700</v>
+        <v>-4000</v>
       </c>
       <c r="G35" s="3">
-        <v>3400</v>
+        <v>0</v>
       </c>
       <c r="H35" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="I35" s="3">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3">
+        <v>0</v>
+      </c>
+      <c r="K35" s="3">
         <v>1900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="L35" s="3">
         <v>3500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="M35" s="3">
         <v>-600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="N35" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1517,8 +1771,11 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1530,269 +1787,353 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>0</v>
+        <v>74900</v>
       </c>
       <c r="E41" s="3">
-        <v>0</v>
+        <v>28500</v>
       </c>
       <c r="F41" s="3">
-        <v>400</v>
+        <v>51700</v>
       </c>
       <c r="G41" s="3">
-        <v>200</v>
+        <v>72700</v>
       </c>
       <c r="H41" s="3">
+        <v>23800</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K41" s="3">
         <v>300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="L41" s="3">
         <v>600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="M41" s="3">
         <v>800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="N41" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>30100</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>35400</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>26000</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3">
-        <v>0</v>
+        <v>9900</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
+        <v>169600</v>
       </c>
       <c r="E43" s="3">
-        <v>0</v>
+        <v>165000</v>
       </c>
       <c r="F43" s="3">
-        <v>0</v>
+        <v>179400</v>
       </c>
       <c r="G43" s="3">
-        <v>0</v>
+        <v>179600</v>
       </c>
       <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+        <v>179400</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3">
+        <v>0</v>
+      </c>
+      <c r="M43" s="3">
+        <v>0</v>
+      </c>
+      <c r="N43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>0</v>
+        <v>44300</v>
       </c>
       <c r="E44" s="3">
-        <v>0</v>
+        <v>44600</v>
       </c>
       <c r="F44" s="3">
-        <v>0</v>
+        <v>37800</v>
       </c>
       <c r="G44" s="3">
-        <v>0</v>
+        <v>41900</v>
       </c>
       <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+        <v>31600</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3">
+        <v>0</v>
+      </c>
+      <c r="M44" s="3">
+        <v>0</v>
+      </c>
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>100</v>
+        <v>5000</v>
       </c>
       <c r="E45" s="3">
-        <v>200</v>
+        <v>4300</v>
       </c>
       <c r="F45" s="3">
-        <v>100</v>
+        <v>3400</v>
       </c>
       <c r="G45" s="3">
-        <v>200</v>
+        <v>3400</v>
       </c>
       <c r="H45" s="3">
+        <v>3000</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K45" s="3">
         <v>300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="L45" s="3">
         <v>500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="M45" s="3">
         <v>500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="N45" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>100</v>
+        <v>324000</v>
       </c>
       <c r="E46" s="3">
-        <v>200</v>
+        <v>277800</v>
       </c>
       <c r="F46" s="3">
-        <v>500</v>
+        <v>298400</v>
       </c>
       <c r="G46" s="3">
-        <v>400</v>
+        <v>307600</v>
       </c>
       <c r="H46" s="3">
+        <v>247800</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K46" s="3">
         <v>600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="L46" s="3">
         <v>1100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="M46" s="3">
         <v>1300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="N46" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>19300</v>
+        <v>200</v>
       </c>
       <c r="E47" s="3">
-        <v>19000</v>
+        <v>1200</v>
       </c>
       <c r="F47" s="3">
-        <v>338400</v>
+        <v>1500</v>
       </c>
       <c r="G47" s="3">
-        <v>335500</v>
+        <v>1800</v>
       </c>
       <c r="H47" s="3">
+        <v>1900</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K47" s="3">
         <v>333900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="L47" s="3">
         <v>333500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="M47" s="3">
         <v>333500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="N47" s="3">
         <v>333500</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>0</v>
+        <v>84400</v>
       </c>
       <c r="E48" s="3">
-        <v>0</v>
+        <v>83800</v>
       </c>
       <c r="F48" s="3">
-        <v>0</v>
+        <v>82400</v>
       </c>
       <c r="G48" s="3">
-        <v>0</v>
+        <v>79100</v>
       </c>
       <c r="H48" s="3">
-        <v>0</v>
-      </c>
-      <c r="I48" s="3">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3">
-        <v>0</v>
+        <v>77400</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L48" s="3">
+        <v>0</v>
+      </c>
+      <c r="M48" s="3">
+        <v>0</v>
+      </c>
+      <c r="N48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="E49" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="F49" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="G49" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="H49" s="3">
-        <v>0</v>
-      </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3">
-        <v>0</v>
+        <v>1200</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1820,8 +2161,17 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1849,37 +2199,55 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>4</v>
+      <c r="D52" s="3">
+        <v>12200</v>
       </c>
       <c r="E52" s="3">
-        <v>0</v>
+        <v>10500</v>
       </c>
       <c r="F52" s="3">
-        <v>0</v>
+        <v>10500</v>
       </c>
       <c r="G52" s="3">
-        <v>0</v>
+        <v>8300</v>
       </c>
       <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
+        <v>7900</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3">
         <v>100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="N52" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1907,37 +2275,55 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>19400</v>
+        <v>421900</v>
       </c>
       <c r="E54" s="3">
-        <v>19200</v>
+        <v>374500</v>
       </c>
       <c r="F54" s="3">
-        <v>338900</v>
+        <v>394000</v>
       </c>
       <c r="G54" s="3">
-        <v>336000</v>
+        <v>398000</v>
       </c>
       <c r="H54" s="3">
+        <v>336200</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K54" s="3">
         <v>334500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="L54" s="3">
         <v>334600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="M54" s="3">
         <v>334900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="N54" s="3">
         <v>335100</v>
       </c>
     </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1949,8 +2335,11 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1962,54 +2351,66 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>3900</v>
+        <v>188300</v>
       </c>
       <c r="E57" s="3">
-        <v>3700</v>
+        <v>127600</v>
       </c>
       <c r="F57" s="3">
-        <v>2600</v>
+        <v>120400</v>
       </c>
       <c r="G57" s="3">
-        <v>1900</v>
+        <v>122200</v>
       </c>
       <c r="H57" s="3">
+        <v>111800</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K57" s="3">
         <v>900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="L57" s="3">
         <v>1000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="M57" s="3">
         <v>1000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="N57" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>200</v>
+        <v>1200</v>
       </c>
       <c r="E58" s="3">
-        <v>200</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>4</v>
+        <v>1200</v>
+      </c>
+      <c r="F58" s="3">
+        <v>600</v>
+      </c>
+      <c r="G58" s="3">
+        <v>600</v>
+      </c>
+      <c r="H58" s="3">
+        <v>400</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>4</v>
@@ -2020,25 +2421,34 @@
       <c r="K58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4600</v>
+        <v>44300</v>
       </c>
       <c r="E59" s="3">
-        <v>3300</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>4</v>
+        <v>40200</v>
+      </c>
+      <c r="F59" s="3">
+        <v>46900</v>
+      </c>
+      <c r="G59" s="3">
+        <v>39500</v>
+      </c>
+      <c r="H59" s="3">
+        <v>34400</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>4</v>
@@ -2049,54 +2459,72 @@
       <c r="K59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>8600</v>
+        <v>233800</v>
       </c>
       <c r="E60" s="3">
-        <v>7100</v>
+        <v>169000</v>
       </c>
       <c r="F60" s="3">
-        <v>2600</v>
+        <v>167900</v>
       </c>
       <c r="G60" s="3">
-        <v>1900</v>
+        <v>162300</v>
       </c>
       <c r="H60" s="3">
+        <v>146600</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K60" s="3">
         <v>900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="L60" s="3">
         <v>1000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="M60" s="3">
         <v>1000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="N60" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>85100</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>85200</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>82600</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>82500</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>82000</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
@@ -2107,37 +2535,55 @@
       <c r="K61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>2300</v>
+        <v>46900</v>
       </c>
       <c r="E62" s="3">
-        <v>13100</v>
+        <v>49500</v>
       </c>
       <c r="F62" s="3">
-        <v>13100</v>
+        <v>50500</v>
       </c>
       <c r="G62" s="3">
-        <v>12700</v>
+        <v>45500</v>
       </c>
       <c r="H62" s="3">
+        <v>47000</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K62" s="3">
         <v>15700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="L62" s="3">
         <v>17500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="M62" s="3">
         <v>21200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="N62" s="3">
         <v>21600</v>
       </c>
     </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2165,8 +2611,17 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2194,8 +2649,17 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2223,37 +2687,55 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>10900</v>
+        <v>524400</v>
       </c>
       <c r="E66" s="3">
-        <v>20200</v>
+        <v>471200</v>
       </c>
       <c r="F66" s="3">
-        <v>15700</v>
+        <v>670400</v>
       </c>
       <c r="G66" s="3">
-        <v>14600</v>
+        <v>290400</v>
       </c>
       <c r="H66" s="3">
+        <v>275600</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K66" s="3">
         <v>16500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="L66" s="3">
         <v>18500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="M66" s="3">
         <v>22300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="N66" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2265,8 +2747,11 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2294,8 +2779,17 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2323,22 +2817,31 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>0</v>
+        <v>65000</v>
       </c>
       <c r="E70" s="3">
-        <v>0</v>
+        <v>65000</v>
       </c>
       <c r="F70" s="3">
-        <v>0</v>
+        <v>65000</v>
       </c>
       <c r="G70" s="3">
-        <v>0</v>
+        <v>62900</v>
       </c>
       <c r="H70" s="3">
         <v>0</v>
@@ -2352,8 +2855,17 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2381,37 +2893,55 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-21400</v>
+        <v>-175600</v>
       </c>
       <c r="E72" s="3">
-        <v>-19700</v>
+        <v>-161800</v>
       </c>
       <c r="F72" s="3">
-        <v>-14200</v>
+        <v>-341400</v>
       </c>
       <c r="G72" s="3">
-        <v>-13500</v>
+        <v>5800</v>
       </c>
       <c r="H72" s="3">
+        <v>24300</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K72" s="3">
         <v>-15600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="L72" s="3">
         <v>-17400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="M72" s="3">
         <v>-20900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="N72" s="3">
         <v>-20300</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2439,8 +2969,17 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2468,8 +3007,17 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2497,37 +3045,55 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>8500</v>
+        <v>-167400</v>
       </c>
       <c r="E76" s="3">
-        <v>-1000</v>
+        <v>-161700</v>
       </c>
       <c r="F76" s="3">
-        <v>323200</v>
+        <v>-341300</v>
       </c>
       <c r="G76" s="3">
-        <v>321400</v>
+        <v>44600</v>
       </c>
       <c r="H76" s="3">
+        <v>60600</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K76" s="3">
         <v>318000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="L76" s="3">
         <v>316100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="M76" s="3">
         <v>312600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="N76" s="3">
         <v>313200</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2555,71 +3121,98 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-1700</v>
+        <v>-7800</v>
       </c>
       <c r="E81" s="3">
-        <v>200</v>
+        <v>-5100</v>
       </c>
       <c r="F81" s="3">
-        <v>1700</v>
+        <v>-4000</v>
       </c>
       <c r="G81" s="3">
-        <v>3400</v>
+        <v>0</v>
       </c>
       <c r="H81" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="I81" s="3">
+        <v>0</v>
+      </c>
+      <c r="J81" s="3">
+        <v>0</v>
+      </c>
+      <c r="K81" s="3">
         <v>1900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="L81" s="3">
         <v>3500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="M81" s="3">
         <v>-600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="N81" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2631,37 +3224,49 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+      <c r="M82" s="3"/>
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="F83" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
+        <v>4300</v>
       </c>
       <c r="H83" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="I83" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2689,8 +3294,17 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2718,8 +3332,17 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2747,8 +3370,17 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2776,8 +3408,17 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2805,37 +3446,55 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-300</v>
+        <v>45100</v>
       </c>
       <c r="E89" s="3">
-        <v>-1000</v>
+        <v>-12000</v>
       </c>
       <c r="F89" s="3">
-        <v>-100</v>
+        <v>-3900</v>
       </c>
       <c r="G89" s="3">
-        <v>-200</v>
+        <v>-2300</v>
       </c>
       <c r="H89" s="3">
         <v>-300</v>
       </c>
       <c r="I89" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="J89" s="3">
+        <v>11600</v>
+      </c>
+      <c r="K89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L89" s="3">
         <v>-200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="M89" s="3">
         <v>-100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="N89" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2847,37 +3506,49 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+      <c r="M90" s="3"/>
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-4100</v>
       </c>
       <c r="E91" s="3">
-        <v>0</v>
+        <v>-2800</v>
       </c>
       <c r="F91" s="3">
-        <v>0</v>
+        <v>-2600</v>
       </c>
       <c r="G91" s="3">
-        <v>0</v>
+        <v>-4100</v>
       </c>
       <c r="H91" s="3">
-        <v>0</v>
+        <v>-2800</v>
       </c>
       <c r="I91" s="3">
-        <v>0</v>
+        <v>-2100</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>-2300</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2905,8 +3576,17 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2934,37 +3614,55 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-100</v>
+        <v>1500</v>
       </c>
       <c r="E94" s="3">
-        <v>321600</v>
+        <v>-10900</v>
       </c>
       <c r="F94" s="3">
-        <v>200</v>
+        <v>-18400</v>
       </c>
       <c r="G94" s="3">
-        <v>100</v>
+        <v>-6300</v>
       </c>
       <c r="H94" s="3">
-        <v>0</v>
+        <v>-2600</v>
       </c>
       <c r="I94" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="J94" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2976,8 +3674,11 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+      <c r="M95" s="3"/>
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3005,8 +3706,17 @@
       <c r="K96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3034,8 +3744,17 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3063,8 +3782,17 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3092,37 +3820,55 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>300</v>
+        <v>-300</v>
       </c>
       <c r="E100" s="3">
-        <v>-321000</v>
+        <v>-300</v>
       </c>
       <c r="F100" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="G100" s="3">
-        <v>0</v>
+        <v>54400</v>
       </c>
       <c r="H100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I100" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="J100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3150,33 +3896,51 @@
       <c r="K101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>46400</v>
       </c>
       <c r="E102" s="3">
-        <v>-400</v>
+        <v>-23100</v>
       </c>
       <c r="F102" s="3">
-        <v>100</v>
+        <v>-21100</v>
       </c>
       <c r="G102" s="3">
+        <v>45800</v>
+      </c>
+      <c r="H102" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="I102" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="J102" s="3">
+        <v>10600</v>
+      </c>
+      <c r="K102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M102" s="3">
         <v>-100</v>
       </c>
-      <c r="H102" s="3">
-        <v>-300</v>
-      </c>
-      <c r="I102" s="3">
-        <v>-200</v>
-      </c>
-      <c r="J102" s="3">
-        <v>-100</v>
-      </c>
-      <c r="K102" s="3">
+      <c r="N102" s="3">
         <v>-100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AONC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AONC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="92">
   <si>
     <t>AONC</t>
   </si>
@@ -656,99 +656,103 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>434000</v>
+      </c>
+      <c r="E8" s="3">
         <v>364300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>324200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>336300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>618700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>303700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>300400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>297300</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
-      </c>
       <c r="L8" s="3">
         <v>0</v>
       </c>
@@ -758,35 +762,38 @@
       <c r="N8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>404600</v>
+      </c>
+      <c r="E9" s="3">
         <v>354900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>315600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>310900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>569900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>278500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>273600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>267600</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>4</v>
       </c>
@@ -796,35 +803,38 @@
       <c r="N9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>29400</v>
+      </c>
+      <c r="E10" s="3">
         <v>9400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>8600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>25400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>48800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>25200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>26800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>29700</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>4</v>
       </c>
@@ -834,8 +844,11 @@
       <c r="N10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -850,8 +863,9 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -888,8 +902,11 @@
       <c r="N12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -926,35 +943,38 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>700</v>
+      </c>
+      <c r="E14" s="3">
         <v>400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>24600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>5300</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K14" s="3">
         <v>200</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
@@ -964,8 +984,11 @@
       <c r="N14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1002,8 +1025,11 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1015,84 +1041,91 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>442000</v>
+      </c>
+      <c r="E17" s="3">
         <v>383600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>344800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>360700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>622800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>304200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>297100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>291200</v>
-      </c>
-      <c r="K17" s="3">
-        <v>300</v>
       </c>
       <c r="L17" s="3">
         <v>300</v>
       </c>
       <c r="M17" s="3">
+        <v>300</v>
+      </c>
+      <c r="N17" s="3">
         <v>900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-19300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-20600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-24400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-4100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>6100</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-300</v>
       </c>
       <c r="L18" s="3">
         <v>-300</v>
       </c>
       <c r="M18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="N18" s="3">
         <v>-900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1107,84 +1140,91 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-4300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>3800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-17800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-18300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-25300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-4100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>4100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>8700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3500</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1192,26 +1232,26 @@
         <v>1800</v>
       </c>
       <c r="E22" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F22" s="3">
         <v>1900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>3000</v>
-      </c>
-      <c r="H22" s="3">
-        <v>1400</v>
       </c>
       <c r="I22" s="3">
         <v>1400</v>
       </c>
       <c r="J22" s="3">
+        <v>1400</v>
+      </c>
+      <c r="K22" s="3">
         <v>900</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
@@ -1221,61 +1261,67 @@
       <c r="N22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-22100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-22300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-28900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-11400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>5600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E24" s="3">
         <v>2900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>300</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
         <v>0</v>
       </c>
@@ -1288,8 +1334,8 @@
       <c r="K24" s="3">
         <v>0</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>4</v>
+      <c r="L24" s="3">
+        <v>0</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>4</v>
@@ -1297,8 +1343,11 @@
       <c r="N24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1335,84 +1384,93 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-25000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-22300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-29200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-11400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>5600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-7800</v>
+        <v>1400</v>
       </c>
       <c r="E27" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="F27" s="3">
         <v>-5100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-4000</v>
       </c>
-      <c r="G27" s="3">
-        <v>0</v>
-      </c>
       <c r="H27" s="3">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3">
         <v>-1500</v>
       </c>
-      <c r="I27" s="3">
-        <v>0</v>
-      </c>
       <c r="J27" s="3">
         <v>0</v>
       </c>
       <c r="K27" s="3">
+        <v>0</v>
+      </c>
+      <c r="L27" s="3">
         <v>1900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1449,8 +1507,11 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1487,8 +1548,11 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1525,8 +1589,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1563,84 +1630,93 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E32" s="3">
         <v>1100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>4300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-3800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-3700</v>
       </c>
     </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-7800</v>
+        <v>1400</v>
       </c>
       <c r="E33" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="F33" s="3">
         <v>-5100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-4000</v>
       </c>
-      <c r="G33" s="3">
-        <v>0</v>
-      </c>
       <c r="H33" s="3">
+        <v>0</v>
+      </c>
+      <c r="I33" s="3">
         <v>-1500</v>
       </c>
-      <c r="I33" s="3">
-        <v>0</v>
-      </c>
       <c r="J33" s="3">
         <v>0</v>
       </c>
       <c r="K33" s="3">
+        <v>0</v>
+      </c>
+      <c r="L33" s="3">
         <v>1900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1677,89 +1753,98 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-7800</v>
+        <v>1400</v>
       </c>
       <c r="E35" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="F35" s="3">
         <v>-5100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-4000</v>
       </c>
-      <c r="G35" s="3">
-        <v>0</v>
-      </c>
       <c r="H35" s="3">
+        <v>0</v>
+      </c>
+      <c r="I35" s="3">
         <v>-1500</v>
       </c>
-      <c r="I35" s="3">
-        <v>0</v>
-      </c>
       <c r="J35" s="3">
         <v>0</v>
       </c>
       <c r="K35" s="3">
+        <v>0</v>
+      </c>
+      <c r="L35" s="3">
         <v>1900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1774,8 +1859,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1790,72 +1876,76 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>33800</v>
+      </c>
+      <c r="E41" s="3">
         <v>74900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>28500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>51700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>72700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>23800</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K41" s="3">
+      <c r="K41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L41" s="3">
         <v>300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E42" s="3">
         <v>30100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>35400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>26000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>10000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>9900</v>
       </c>
-      <c r="I42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
+      <c r="K42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L42" s="3">
         <v>0</v>
@@ -1866,34 +1956,37 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>188500</v>
+      </c>
+      <c r="E43" s="3">
         <v>169600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>165000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>179400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>179600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>179400</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -1904,34 +1997,37 @@
       <c r="N43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>54300</v>
+      </c>
+      <c r="E44" s="3">
         <v>44300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>44600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>37800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>41900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>31600</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -1942,37 +2038,40 @@
       <c r="N44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E45" s="3">
         <v>5000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4300</v>
-      </c>
-      <c r="F45" s="3">
-        <v>3400</v>
       </c>
       <c r="G45" s="3">
         <v>3400</v>
       </c>
       <c r="H45" s="3">
+        <v>3400</v>
+      </c>
+      <c r="I45" s="3">
         <v>3000</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L45" s="3">
         <v>300</v>
-      </c>
-      <c r="L45" s="3">
-        <v>500</v>
       </c>
       <c r="M45" s="3">
         <v>500</v>
@@ -1980,75 +2079,81 @@
       <c r="N45" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O45" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>306300</v>
+      </c>
+      <c r="E46" s="3">
         <v>324000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>277800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>298400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>307600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>247800</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K46" s="3">
+      <c r="K46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L46" s="3">
         <v>600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>0</v>
+      </c>
+      <c r="E47" s="3">
         <v>200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1900</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L47" s="3">
         <v>333900</v>
-      </c>
-      <c r="L47" s="3">
-        <v>333500</v>
       </c>
       <c r="M47" s="3">
         <v>333500</v>
@@ -2056,34 +2161,37 @@
       <c r="N47" s="3">
         <v>333500</v>
       </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3">
+        <v>333500</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>93100</v>
+      </c>
+      <c r="E48" s="3">
         <v>84400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>83800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>82400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>79100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>77400</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K48" s="3">
-        <v>0</v>
+      <c r="K48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L48" s="3">
         <v>0</v>
@@ -2094,13 +2202,16 @@
       <c r="N48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1200</v>
+        <v>13400</v>
       </c>
       <c r="E49" s="3">
         <v>1200</v>
@@ -2114,14 +2225,14 @@
       <c r="H49" s="3">
         <v>1200</v>
       </c>
-      <c r="I49" s="3" t="s">
-        <v>4</v>
+      <c r="I49" s="3">
+        <v>1200</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
+      <c r="K49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L49" s="3">
         <v>0</v>
@@ -2132,8 +2243,11 @@
       <c r="N49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2170,8 +2284,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2208,46 +2325,52 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E52" s="3">
         <v>12200</v>
-      </c>
-      <c r="E52" s="3">
-        <v>10500</v>
       </c>
       <c r="F52" s="3">
         <v>10500</v>
       </c>
       <c r="G52" s="3">
+        <v>10500</v>
+      </c>
+      <c r="H52" s="3">
         <v>8300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>7900</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
       </c>
       <c r="M52" s="3">
+        <v>0</v>
+      </c>
+      <c r="N52" s="3">
         <v>100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2284,46 +2407,52 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>430800</v>
+      </c>
+      <c r="E54" s="3">
         <v>421900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>374500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>394000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>398000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>336200</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K54" s="3">
+      <c r="K54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L54" s="3">
         <v>334500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>334600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>334900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>335100</v>
       </c>
     </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2338,8 +2467,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2354,67 +2484,71 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>189500</v>
+      </c>
+      <c r="E57" s="3">
         <v>188300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>127600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>120400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>122200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>111800</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K57" s="3">
+      <c r="K57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L57" s="3">
         <v>900</v>
-      </c>
-      <c r="L57" s="3">
-        <v>1000</v>
       </c>
       <c r="M57" s="3">
         <v>1000</v>
       </c>
       <c r="N57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="O57" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1200</v>
+        <v>5100</v>
       </c>
       <c r="E58" s="3">
         <v>1200</v>
       </c>
       <c r="F58" s="3">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="G58" s="3">
         <v>600</v>
       </c>
       <c r="H58" s="3">
+        <v>600</v>
+      </c>
+      <c r="I58" s="3">
         <v>400</v>
       </c>
-      <c r="I58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J58" s="3" t="s">
         <v>4</v>
       </c>
@@ -2430,29 +2564,32 @@
       <c r="N58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>37000</v>
+      </c>
+      <c r="E59" s="3">
         <v>44300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>40200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>46900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>39500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>34400</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>4</v>
       </c>
@@ -2468,67 +2605,73 @@
       <c r="N59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>231600</v>
+      </c>
+      <c r="E60" s="3">
         <v>233800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>169000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>167900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>162300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>146600</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K60" s="3">
+      <c r="K60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L60" s="3">
         <v>900</v>
-      </c>
-      <c r="L60" s="3">
-        <v>1000</v>
       </c>
       <c r="M60" s="3">
         <v>1000</v>
       </c>
       <c r="N60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="O60" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>92300</v>
+      </c>
+      <c r="E61" s="3">
         <v>85100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>85200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>82600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>82500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>82000</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -2544,46 +2687,52 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>53100</v>
+      </c>
+      <c r="E62" s="3">
         <v>46900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>49500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>50500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>45500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>47000</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L62" s="3">
         <v>15700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>17500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>21200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>21600</v>
       </c>
     </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2620,8 +2769,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2658,8 +2810,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2696,46 +2851,52 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>405800</v>
+      </c>
+      <c r="E66" s="3">
         <v>524400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>471200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>670400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>290400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>275600</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K66" s="3">
+      <c r="K66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L66" s="3">
         <v>16500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>18500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>22300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2750,8 +2911,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2788,8 +2950,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2826,8 +2991,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2841,11 +3009,11 @@
         <v>65000</v>
       </c>
       <c r="G70" s="3">
+        <v>65000</v>
+      </c>
+      <c r="H70" s="3">
         <v>62900</v>
       </c>
-      <c r="H70" s="3">
-        <v>0</v>
-      </c>
       <c r="I70" s="3">
         <v>0</v>
       </c>
@@ -2864,8 +3032,11 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2902,46 +3073,52 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-66700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-175600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-161800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-341400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>5800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>24300</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L72" s="3">
         <v>-15600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-17400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-20900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-20300</v>
       </c>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2978,8 +3155,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3016,8 +3196,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3054,46 +3237,52 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-40000</v>
+      </c>
+      <c r="E76" s="3">
         <v>-167400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-161700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-341300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>44600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>60600</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K76" s="3">
+      <c r="K76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L76" s="3">
         <v>318000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>316100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>312600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>313200</v>
       </c>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3130,89 +3319,98 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-7800</v>
+        <v>1400</v>
       </c>
       <c r="E81" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="F81" s="3">
         <v>-5100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-4000</v>
       </c>
-      <c r="G81" s="3">
-        <v>0</v>
-      </c>
       <c r="H81" s="3">
+        <v>0</v>
+      </c>
+      <c r="I81" s="3">
         <v>-1500</v>
       </c>
-      <c r="I81" s="3">
-        <v>0</v>
-      </c>
       <c r="J81" s="3">
         <v>0</v>
       </c>
       <c r="K81" s="3">
+        <v>0</v>
+      </c>
+      <c r="L81" s="3">
         <v>1900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3227,35 +3425,36 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E83" s="3">
         <v>2500</v>
-      </c>
-      <c r="E83" s="3">
-        <v>2100</v>
       </c>
       <c r="F83" s="3">
         <v>2100</v>
       </c>
       <c r="G83" s="3">
+        <v>2100</v>
+      </c>
+      <c r="H83" s="3">
         <v>4300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2200</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
       <c r="L83" s="3">
         <v>0</v>
       </c>
@@ -3265,8 +3464,11 @@
       <c r="N83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3303,8 +3505,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3341,8 +3546,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3379,8 +3587,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3417,8 +3628,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3455,46 +3669,52 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-33900</v>
+      </c>
+      <c r="E89" s="3">
         <v>45100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-12000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-3900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-8400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>11600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-200</v>
-      </c>
-      <c r="M89" s="3">
-        <v>-100</v>
       </c>
       <c r="N89" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O89" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3509,35 +3729,36 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2300</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
@@ -3547,8 +3768,11 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3585,8 +3809,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3623,34 +3850,37 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E94" s="3">
         <v>1500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-10900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-18400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-6300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2600</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-900</v>
       </c>
       <c r="J94" s="3">
         <v>-900</v>
       </c>
       <c r="K94" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="L94" s="3">
         <v>0</v>
@@ -3661,8 +3891,11 @@
       <c r="N94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3677,8 +3910,9 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3715,8 +3949,11 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3753,8 +3990,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3791,8 +4031,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3829,35 +4072,38 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-300</v>
+        <v>-5500</v>
       </c>
       <c r="E100" s="3">
         <v>-300</v>
       </c>
       <c r="F100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G100" s="3">
         <v>1200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>54400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-100</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
         <v>0</v>
       </c>
@@ -3867,8 +4113,11 @@
       <c r="N100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3905,42 +4154,48 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-41100</v>
+      </c>
+      <c r="E102" s="3">
         <v>46400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-23100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-21100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>45800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-3100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-9800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>10600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AONC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AONC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="92">
   <si>
     <t>AONC</t>
   </si>
@@ -656,106 +656,110 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>470300</v>
+      </c>
+      <c r="E8" s="3">
         <v>434000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>364300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>324200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>336300</v>
       </c>
-      <c r="H8" s="3">
-        <v>618700</v>
-      </c>
       <c r="I8" s="3">
+        <v>315000</v>
+      </c>
+      <c r="J8" s="3">
         <v>303700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>300400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>297300</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
-      </c>
       <c r="M8" s="3">
         <v>0</v>
       </c>
@@ -765,38 +769,41 @@
       <c r="O8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>433700</v>
+      </c>
+      <c r="E9" s="3">
         <v>404600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>354900</v>
       </c>
-      <c r="F9" s="3">
-        <v>315600</v>
-      </c>
       <c r="G9" s="3">
+        <v>312800</v>
+      </c>
+      <c r="H9" s="3">
         <v>310900</v>
       </c>
-      <c r="H9" s="3">
-        <v>569900</v>
-      </c>
       <c r="I9" s="3">
+        <v>291400</v>
+      </c>
+      <c r="J9" s="3">
         <v>278500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>273600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>267600</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>4</v>
       </c>
@@ -806,38 +813,41 @@
       <c r="O9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>36500</v>
+      </c>
+      <c r="E10" s="3">
         <v>29400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>9400</v>
       </c>
-      <c r="F10" s="3">
-        <v>8600</v>
-      </c>
       <c r="G10" s="3">
+        <v>11300</v>
+      </c>
+      <c r="H10" s="3">
         <v>25400</v>
       </c>
-      <c r="H10" s="3">
-        <v>48800</v>
-      </c>
       <c r="I10" s="3">
+        <v>23600</v>
+      </c>
+      <c r="J10" s="3">
         <v>25200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>26800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>29700</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>4</v>
       </c>
@@ -847,8 +857,11 @@
       <c r="O10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -864,8 +877,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -905,8 +919,11 @@
       <c r="O12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -946,38 +963,41 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>700</v>
+        <v>200</v>
       </c>
       <c r="E14" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F14" s="3">
         <v>400</v>
       </c>
-      <c r="F14" s="3">
-        <v>1400</v>
-      </c>
       <c r="G14" s="3">
-        <v>24600</v>
+        <v>-3800</v>
       </c>
       <c r="H14" s="3">
-        <v>5300</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K14" s="3">
+        <v>9100</v>
+      </c>
+      <c r="I14" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="J14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L14" s="3">
         <v>200</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
@@ -987,31 +1007,34 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>2600</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1028,8 +1051,11 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1042,90 +1068,97 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>442000</v>
+        <v>468500</v>
       </c>
       <c r="E17" s="3">
-        <v>383600</v>
+        <v>441300</v>
       </c>
       <c r="F17" s="3">
-        <v>344800</v>
+        <v>383200</v>
       </c>
       <c r="G17" s="3">
-        <v>360700</v>
+        <v>343400</v>
       </c>
       <c r="H17" s="3">
-        <v>622800</v>
+        <v>336100</v>
       </c>
       <c r="I17" s="3">
-        <v>304200</v>
+        <v>315300</v>
       </c>
       <c r="J17" s="3">
+        <v>302300</v>
+      </c>
+      <c r="K17" s="3">
         <v>297100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>291200</v>
-      </c>
-      <c r="L17" s="3">
-        <v>300</v>
       </c>
       <c r="M17" s="3">
         <v>300</v>
       </c>
       <c r="N17" s="3">
+        <v>300</v>
+      </c>
+      <c r="O17" s="3">
         <v>900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-8000</v>
+        <v>1800</v>
       </c>
       <c r="E18" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-18900</v>
+      </c>
+      <c r="G18" s="3">
         <v>-19300</v>
       </c>
-      <c r="F18" s="3">
-        <v>-20600</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-24400</v>
-      </c>
       <c r="H18" s="3">
-        <v>-4100</v>
+        <v>200</v>
       </c>
       <c r="I18" s="3">
-        <v>-500</v>
+        <v>-300</v>
       </c>
       <c r="J18" s="3">
+        <v>1500</v>
+      </c>
+      <c r="K18" s="3">
         <v>3300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>6100</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-300</v>
       </c>
       <c r="M18" s="3">
         <v>-300</v>
       </c>
       <c r="N18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O18" s="3">
         <v>-900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1141,120 +1174,127 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>6600</v>
+        <v>1600</v>
       </c>
       <c r="E20" s="3">
-        <v>-1100</v>
+        <v>-4300</v>
       </c>
       <c r="F20" s="3">
-        <v>200</v>
+        <v>1900</v>
       </c>
       <c r="G20" s="3">
-        <v>-2900</v>
+        <v>5800</v>
       </c>
       <c r="H20" s="3">
-        <v>-4300</v>
+        <v>3300</v>
       </c>
       <c r="I20" s="3">
-        <v>600</v>
+        <v>5000</v>
       </c>
       <c r="J20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K20" s="3">
         <v>-500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>3800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>900</v>
+        <v>2700</v>
       </c>
       <c r="E21" s="3">
-        <v>-17800</v>
+        <v>-600</v>
       </c>
       <c r="F21" s="3">
-        <v>-18300</v>
+        <v>-18200</v>
       </c>
       <c r="G21" s="3">
-        <v>-25300</v>
+        <v>-23000</v>
       </c>
       <c r="H21" s="3">
-        <v>-4100</v>
+        <v>-1100</v>
       </c>
       <c r="I21" s="3">
-        <v>2200</v>
+        <v>-3200</v>
       </c>
       <c r="J21" s="3">
         <v>4100</v>
       </c>
       <c r="K21" s="3">
+        <v>4100</v>
+      </c>
+      <c r="L21" s="3">
         <v>8700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3500</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>1800</v>
+        <v>1900</v>
       </c>
       <c r="E22" s="3">
         <v>1800</v>
       </c>
       <c r="F22" s="3">
+        <v>1800</v>
+      </c>
+      <c r="G22" s="3">
         <v>1900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1500</v>
       </c>
-      <c r="H22" s="3">
-        <v>3000</v>
-      </c>
       <c r="I22" s="3">
-        <v>1400</v>
+        <v>1600</v>
       </c>
       <c r="J22" s="3">
         <v>1400</v>
       </c>
       <c r="K22" s="3">
+        <v>1400</v>
+      </c>
+      <c r="L22" s="3">
         <v>900</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
@@ -1264,72 +1304,78 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-3300</v>
+        <v>-1300</v>
       </c>
       <c r="E23" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="F23" s="3">
         <v>-22100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-22300</v>
       </c>
-      <c r="G23" s="3">
-        <v>-28900</v>
-      </c>
       <c r="H23" s="3">
-        <v>-11400</v>
+        <v>-13400</v>
       </c>
       <c r="I23" s="3">
-        <v>-1400</v>
+        <v>1500</v>
       </c>
       <c r="J23" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="K23" s="3">
         <v>1400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>5600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" s="3">
         <v>-300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>300</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
         <v>0</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="J24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1337,8 +1383,8 @@
       <c r="L24" s="3">
         <v>0</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>4</v>
+      <c r="M24" s="3">
+        <v>0</v>
       </c>
       <c r="N24" s="3" t="s">
         <v>4</v>
@@ -1346,8 +1392,11 @@
       <c r="O24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1387,90 +1436,99 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-2900</v>
+        <v>-1300</v>
       </c>
       <c r="E26" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="F26" s="3">
         <v>-25000</v>
       </c>
-      <c r="F26" s="3">
-        <v>-22300</v>
-      </c>
       <c r="G26" s="3">
-        <v>-29200</v>
+        <v>-22400</v>
       </c>
       <c r="H26" s="3">
-        <v>-11400</v>
+        <v>-13700</v>
       </c>
       <c r="I26" s="3">
-        <v>-1400</v>
+        <v>1500</v>
       </c>
       <c r="J26" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="K26" s="3">
         <v>1400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>5600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E27" s="3">
         <v>1400</v>
       </c>
-      <c r="E27" s="3">
-        <v>-8300</v>
-      </c>
       <c r="F27" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="G27" s="3">
         <v>-5100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-4000</v>
       </c>
-      <c r="H27" s="3">
-        <v>0</v>
-      </c>
       <c r="I27" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J27" s="3">
         <v>-1500</v>
       </c>
-      <c r="J27" s="3">
-        <v>0</v>
-      </c>
       <c r="K27" s="3">
         <v>0</v>
       </c>
       <c r="L27" s="3">
+        <v>0</v>
+      </c>
+      <c r="M27" s="3">
         <v>1900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1510,8 +1568,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1551,8 +1612,11 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1592,8 +1656,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1633,90 +1700,99 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-6600</v>
+        <v>-1600</v>
       </c>
       <c r="E32" s="3">
-        <v>1100</v>
+        <v>4300</v>
       </c>
       <c r="F32" s="3">
-        <v>-200</v>
+        <v>-1900</v>
       </c>
       <c r="G32" s="3">
-        <v>2900</v>
+        <v>-5800</v>
       </c>
       <c r="H32" s="3">
-        <v>4300</v>
+        <v>-3300</v>
       </c>
       <c r="I32" s="3">
-        <v>-600</v>
+        <v>-5000</v>
       </c>
       <c r="J32" s="3">
+        <v>400</v>
+      </c>
+      <c r="K32" s="3">
         <v>500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-3800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-3700</v>
       </c>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1400</v>
+        <v>-1100</v>
       </c>
       <c r="E33" s="3">
-        <v>-8300</v>
+        <v>3600</v>
       </c>
       <c r="F33" s="3">
-        <v>-5100</v>
+        <v>-7800</v>
       </c>
       <c r="G33" s="3">
-        <v>-4000</v>
+        <v>-3800</v>
       </c>
       <c r="H33" s="3">
-        <v>0</v>
+        <v>-1800</v>
       </c>
       <c r="I33" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J33" s="3">
         <v>-1500</v>
       </c>
-      <c r="J33" s="3">
-        <v>0</v>
-      </c>
       <c r="K33" s="3">
         <v>0</v>
       </c>
       <c r="L33" s="3">
+        <v>0</v>
+      </c>
+      <c r="M33" s="3">
         <v>1900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1756,95 +1832,104 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1400</v>
+        <v>-1100</v>
       </c>
       <c r="E35" s="3">
-        <v>-8300</v>
+        <v>3600</v>
       </c>
       <c r="F35" s="3">
-        <v>-5100</v>
+        <v>-7800</v>
       </c>
       <c r="G35" s="3">
-        <v>-4000</v>
+        <v>-3800</v>
       </c>
       <c r="H35" s="3">
-        <v>0</v>
+        <v>-1800</v>
       </c>
       <c r="I35" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J35" s="3">
         <v>-1500</v>
       </c>
-      <c r="J35" s="3">
-        <v>0</v>
-      </c>
       <c r="K35" s="3">
         <v>0</v>
       </c>
       <c r="L35" s="3">
+        <v>0</v>
+      </c>
+      <c r="M35" s="3">
         <v>1900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1860,8 +1945,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1877,78 +1963,82 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>19400</v>
+      </c>
+      <c r="E41" s="3">
         <v>33800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>74900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>28500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>51700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>72700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>23800</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L41" s="3">
+      <c r="L41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M41" s="3">
         <v>300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>21400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>30100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>35400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>26000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>10000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>9900</v>
       </c>
-      <c r="J42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
+      <c r="L42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M42" s="3">
         <v>0</v>
@@ -1959,37 +2049,40 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>193100</v>
+      </c>
+      <c r="E43" s="3">
         <v>188500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>169600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>165000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>179400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>179600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>179400</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -2000,37 +2093,40 @@
       <c r="O43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>49300</v>
+      </c>
+      <c r="E44" s="3">
         <v>54300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>44300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>44600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>37800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>41900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>31600</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2041,28 +2137,31 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>8300</v>
-      </c>
-      <c r="E45" s="3">
-        <v>5000</v>
-      </c>
-      <c r="F45" s="3">
-        <v>4300</v>
-      </c>
-      <c r="G45" s="3">
-        <v>3400</v>
-      </c>
-      <c r="H45" s="3">
-        <v>3400</v>
-      </c>
-      <c r="I45" s="3">
-        <v>3000</v>
+      <c r="D45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>4</v>
@@ -2070,11 +2169,11 @@
       <c r="K45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M45" s="3">
         <v>300</v>
-      </c>
-      <c r="M45" s="3">
-        <v>500</v>
       </c>
       <c r="N45" s="3">
         <v>500</v>
@@ -2082,69 +2181,75 @@
       <c r="O45" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>271200</v>
+      </c>
+      <c r="E46" s="3">
         <v>306300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>324000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>277800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>298400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>307600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>247800</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L46" s="3">
+      <c r="L46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M46" s="3">
         <v>600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>200</v>
-      </c>
-      <c r="F47" s="3">
-        <v>1200</v>
-      </c>
-      <c r="G47" s="3">
-        <v>1500</v>
-      </c>
-      <c r="H47" s="3">
-        <v>1800</v>
-      </c>
-      <c r="I47" s="3">
-        <v>1900</v>
+      <c r="D47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>4</v>
@@ -2152,11 +2257,11 @@
       <c r="K47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M47" s="3">
         <v>333900</v>
-      </c>
-      <c r="M47" s="3">
-        <v>333500</v>
       </c>
       <c r="N47" s="3">
         <v>333500</v>
@@ -2164,37 +2269,40 @@
       <c r="O47" s="3">
         <v>333500</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>333500</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>91000</v>
+      </c>
+      <c r="E48" s="3">
         <v>93100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>84400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>83800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>82400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>79100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>77400</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L48" s="3">
-        <v>0</v>
+      <c r="L48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M48" s="3">
         <v>0</v>
@@ -2205,8 +2313,11 @@
       <c r="O48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2214,7 +2325,7 @@
         <v>13400</v>
       </c>
       <c r="E49" s="3">
-        <v>1200</v>
+        <v>13400</v>
       </c>
       <c r="F49" s="3">
         <v>1200</v>
@@ -2228,14 +2339,14 @@
       <c r="I49" s="3">
         <v>1200</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>4</v>
+      <c r="J49" s="3">
+        <v>1200</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
+      <c r="L49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M49" s="3">
         <v>0</v>
@@ -2246,8 +2357,11 @@
       <c r="O49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2287,8 +2401,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2328,49 +2445,55 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>18800</v>
+      </c>
+      <c r="E52" s="3">
         <v>18000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>12200</v>
       </c>
-      <c r="F52" s="3">
-        <v>10500</v>
-      </c>
       <c r="G52" s="3">
-        <v>10500</v>
+        <v>7600</v>
       </c>
       <c r="H52" s="3">
+        <v>7100</v>
+      </c>
+      <c r="I52" s="3">
         <v>8300</v>
       </c>
-      <c r="I52" s="3">
-        <v>7900</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>4</v>
+      <c r="J52" s="3">
+        <v>7100</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
+      <c r="L52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
       </c>
       <c r="N52" s="3">
+        <v>0</v>
+      </c>
+      <c r="O52" s="3">
         <v>100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2410,49 +2533,55 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>394800</v>
+      </c>
+      <c r="E54" s="3">
         <v>430800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>421900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>374500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>394000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>398000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>336200</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L54" s="3">
+      <c r="L54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M54" s="3">
         <v>334500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>334600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>334900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>335100</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2468,8 +2597,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2485,72 +2615,76 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>155500</v>
+      </c>
+      <c r="E57" s="3">
         <v>189500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>188300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>127600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>120400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>122200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>111800</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L57" s="3">
+      <c r="L57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M57" s="3">
         <v>900</v>
-      </c>
-      <c r="M57" s="3">
-        <v>1000</v>
       </c>
       <c r="N57" s="3">
         <v>1000</v>
       </c>
       <c r="O57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="P57" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>5100</v>
+        <v>12400</v>
       </c>
       <c r="E58" s="3">
-        <v>1200</v>
+        <v>12500</v>
       </c>
       <c r="F58" s="3">
-        <v>1200</v>
+        <v>7900</v>
       </c>
       <c r="G58" s="3">
-        <v>600</v>
+        <v>7900</v>
       </c>
       <c r="H58" s="3">
-        <v>600</v>
+        <v>7800</v>
       </c>
       <c r="I58" s="3">
-        <v>400</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>4</v>
+        <v>7700</v>
+      </c>
+      <c r="J58" s="3">
+        <v>7500</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>4</v>
@@ -2567,31 +2701,34 @@
       <c r="O58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>37000</v>
+        <v>11100</v>
       </c>
       <c r="E59" s="3">
-        <v>44300</v>
+        <v>12100</v>
       </c>
       <c r="F59" s="3">
-        <v>40200</v>
+        <v>18800</v>
       </c>
       <c r="G59" s="3">
-        <v>46900</v>
+        <v>16000</v>
       </c>
       <c r="H59" s="3">
-        <v>39500</v>
+        <v>15700</v>
       </c>
       <c r="I59" s="3">
-        <v>34400</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>4</v>
+        <v>19600</v>
+      </c>
+      <c r="J59" s="3">
+        <v>14800</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>4</v>
@@ -2608,72 +2745,78 @@
       <c r="O59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>199900</v>
+      </c>
+      <c r="E60" s="3">
         <v>231600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>233800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>169000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>167900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>162300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>146600</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L60" s="3">
+      <c r="L60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M60" s="3">
         <v>900</v>
-      </c>
-      <c r="M60" s="3">
-        <v>1000</v>
       </c>
       <c r="N60" s="3">
         <v>1000</v>
       </c>
       <c r="O60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="P60" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>92300</v>
+        <v>135000</v>
       </c>
       <c r="E61" s="3">
-        <v>85100</v>
+        <v>138400</v>
       </c>
       <c r="F61" s="3">
-        <v>85200</v>
+        <v>124900</v>
       </c>
       <c r="G61" s="3">
-        <v>82600</v>
+        <v>125000</v>
       </c>
       <c r="H61" s="3">
-        <v>82500</v>
+        <v>124800</v>
       </c>
       <c r="I61" s="3">
-        <v>82000</v>
+        <v>122000</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>123000</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -2690,49 +2833,55 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>53100</v>
+        <v>5900</v>
       </c>
       <c r="E62" s="3">
-        <v>46900</v>
+        <v>6900</v>
       </c>
       <c r="F62" s="3">
-        <v>49500</v>
+        <v>7100</v>
       </c>
       <c r="G62" s="3">
-        <v>50500</v>
+        <v>9700</v>
       </c>
       <c r="H62" s="3">
-        <v>45500</v>
+        <v>8200</v>
       </c>
       <c r="I62" s="3">
-        <v>47000</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>4</v>
+        <v>6000</v>
+      </c>
+      <c r="J62" s="3">
+        <v>6100</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M62" s="3">
         <v>15700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>17500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>21200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>21600</v>
       </c>
     </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2772,8 +2921,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2813,8 +2965,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2854,49 +3009,55 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>405800</v>
+        <v>340700</v>
       </c>
       <c r="E66" s="3">
-        <v>524400</v>
+        <v>376900</v>
       </c>
       <c r="F66" s="3">
-        <v>471200</v>
+        <v>365800</v>
       </c>
       <c r="G66" s="3">
-        <v>670400</v>
+        <v>303700</v>
       </c>
       <c r="H66" s="3">
-        <v>290400</v>
+        <v>300900</v>
       </c>
       <c r="I66" s="3">
+        <v>290300</v>
+      </c>
+      <c r="J66" s="3">
         <v>275600</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L66" s="3">
+      <c r="L66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M66" s="3">
         <v>16500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>18500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>22300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2912,8 +3073,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2953,8 +3115,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2994,8 +3159,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3012,11 +3180,11 @@
         <v>65000</v>
       </c>
       <c r="H70" s="3">
+        <v>65000</v>
+      </c>
+      <c r="I70" s="3">
         <v>62900</v>
       </c>
-      <c r="I70" s="3">
-        <v>0</v>
-      </c>
       <c r="J70" s="3">
         <v>0</v>
       </c>
@@ -3035,8 +3203,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3076,49 +3247,55 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-103500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-66700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-175600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-161800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-341400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>5800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>24300</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M72" s="3">
         <v>-15600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-17400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-20900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-20300</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3158,8 +3335,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3199,8 +3379,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3240,49 +3423,55 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-103800</v>
+      </c>
+      <c r="E76" s="3">
         <v>-40000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-167400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-161700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-341300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>44600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>60600</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L76" s="3">
+      <c r="L76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M76" s="3">
         <v>318000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>316100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>312600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>313200</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3322,95 +3511,104 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1400</v>
+        <v>-1100</v>
       </c>
       <c r="E81" s="3">
-        <v>-8300</v>
+        <v>3600</v>
       </c>
       <c r="F81" s="3">
-        <v>-5100</v>
+        <v>-7800</v>
       </c>
       <c r="G81" s="3">
-        <v>-4000</v>
+        <v>-3800</v>
       </c>
       <c r="H81" s="3">
-        <v>0</v>
+        <v>-1800</v>
       </c>
       <c r="I81" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J81" s="3">
         <v>-1500</v>
       </c>
-      <c r="J81" s="3">
-        <v>0</v>
-      </c>
       <c r="K81" s="3">
         <v>0</v>
       </c>
       <c r="L81" s="3">
+        <v>0</v>
+      </c>
+      <c r="M81" s="3">
         <v>1900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3426,38 +3624,39 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>2400</v>
+        <v>3900</v>
       </c>
       <c r="E83" s="3">
-        <v>2500</v>
+        <v>4200</v>
       </c>
       <c r="F83" s="3">
-        <v>2100</v>
+        <v>4400</v>
       </c>
       <c r="G83" s="3">
-        <v>2100</v>
+        <v>4000</v>
       </c>
       <c r="H83" s="3">
-        <v>4300</v>
+        <v>4800</v>
       </c>
       <c r="I83" s="3">
+        <v>4200</v>
+      </c>
+      <c r="J83" s="3">
+        <v>4100</v>
+      </c>
+      <c r="K83" s="3">
+        <v>1400</v>
+      </c>
+      <c r="L83" s="3">
         <v>2200</v>
       </c>
-      <c r="J83" s="3">
-        <v>1400</v>
-      </c>
-      <c r="K83" s="3">
-        <v>2200</v>
-      </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
       <c r="M83" s="3">
         <v>0</v>
       </c>
@@ -3467,8 +3666,11 @@
       <c r="O83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3508,8 +3710,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3549,8 +3754,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3590,8 +3798,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3631,8 +3842,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3672,49 +3886,55 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-28100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-33900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>45100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-12000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-3900</v>
       </c>
-      <c r="H89" s="3">
-        <v>-2300</v>
-      </c>
       <c r="I89" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="J89" s="3">
         <v>-300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-8400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>11600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-200</v>
-      </c>
-      <c r="N89" s="3">
-        <v>-100</v>
       </c>
       <c r="O89" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3730,38 +3950,39 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2300</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
@@ -3771,8 +3992,11 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3812,8 +4036,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3853,37 +4080,40 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>1500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-10900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-18400</v>
       </c>
-      <c r="H94" s="3">
-        <v>-6300</v>
-      </c>
       <c r="I94" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="J94" s="3">
         <v>-2600</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-900</v>
       </c>
       <c r="K94" s="3">
         <v>-900</v>
       </c>
       <c r="L94" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="M94" s="3">
         <v>0</v>
@@ -3894,8 +4124,11 @@
       <c r="O94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3911,31 +4144,32 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -3952,8 +4186,11 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3993,8 +4230,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4034,8 +4274,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4075,38 +4318,41 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-5500</v>
-      </c>
-      <c r="E100" s="3">
-        <v>-300</v>
       </c>
       <c r="F100" s="3">
         <v>-300</v>
       </c>
       <c r="G100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H100" s="3">
         <v>1200</v>
       </c>
-      <c r="H100" s="3">
-        <v>54400</v>
-      </c>
       <c r="I100" s="3">
+        <v>54500</v>
+      </c>
+      <c r="J100" s="3">
         <v>-100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-100</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
         <v>0</v>
       </c>
@@ -4116,31 +4362,34 @@
       <c r="O100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -4157,45 +4406,51 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-41100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>46400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-23100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-21100</v>
       </c>
-      <c r="H102" s="3">
-        <v>45800</v>
-      </c>
       <c r="I102" s="3">
+        <v>48900</v>
+      </c>
+      <c r="J102" s="3">
         <v>-3100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-9800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>10600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AONC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AONC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="92">
   <si>
     <t>AONC</t>
   </si>
@@ -656,113 +656,116 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>490900</v>
+      </c>
+      <c r="E8" s="3">
         <v>470300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>434000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>364300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>324200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>336300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>315000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>303700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>300400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>297300</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
-      </c>
       <c r="N8" s="3">
         <v>0</v>
       </c>
@@ -772,41 +775,44 @@
       <c r="P8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>445700</v>
+      </c>
+      <c r="E9" s="3">
         <v>433700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>404600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>354900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>312800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>310900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>291400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>278500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>273600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>267600</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>4</v>
       </c>
@@ -816,41 +822,44 @@
       <c r="P9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>45200</v>
+      </c>
+      <c r="E10" s="3">
         <v>36500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>29400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>9400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>11300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>25400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>23600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>25200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>26800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>29700</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>4</v>
       </c>
@@ -860,8 +869,11 @@
       <c r="P10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -878,8 +890,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -922,8 +935,11 @@
       <c r="P12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -966,41 +982,44 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>700</v>
+      </c>
+      <c r="E14" s="3">
         <v>200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>400</v>
       </c>
-      <c r="G14" s="3">
-        <v>-3800</v>
-      </c>
       <c r="H14" s="3">
+        <v>1400</v>
+      </c>
+      <c r="I14" s="3">
         <v>9100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-8300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2000</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="3">
         <v>200</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
@@ -1010,22 +1029,25 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E15" s="3">
         <v>2600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2500</v>
-      </c>
-      <c r="G15" s="3">
-        <v>2100</v>
       </c>
       <c r="H15" s="3">
         <v>2100</v>
@@ -1034,11 +1056,11 @@
         <v>2100</v>
       </c>
       <c r="J15" s="3">
+        <v>2100</v>
+      </c>
+      <c r="K15" s="3">
         <v>2200</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1054,8 +1076,11 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1069,96 +1094,103 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>482500</v>
+      </c>
+      <c r="E17" s="3">
         <v>468500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>441300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>383200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>343400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>336100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>315300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>302300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>297100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>291200</v>
-      </c>
-      <c r="M17" s="3">
-        <v>300</v>
       </c>
       <c r="N17" s="3">
         <v>300</v>
       </c>
       <c r="O17" s="3">
+        <v>300</v>
+      </c>
+      <c r="P17" s="3">
         <v>900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E18" s="3">
         <v>1800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-7300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-18900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-19300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>6100</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-300</v>
       </c>
       <c r="N18" s="3">
         <v>-300</v>
       </c>
       <c r="O18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P18" s="3">
         <v>-900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1175,129 +1207,136 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E20" s="3">
         <v>1600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-4300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1900</v>
       </c>
-      <c r="G20" s="3">
-        <v>5800</v>
-      </c>
       <c r="H20" s="3">
+        <v>600</v>
+      </c>
+      <c r="I20" s="3">
         <v>3300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>5000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>3800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E21" s="3">
         <v>2700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-18200</v>
       </c>
-      <c r="G21" s="3">
-        <v>-23000</v>
-      </c>
       <c r="H21" s="3">
+        <v>-17800</v>
+      </c>
+      <c r="I21" s="3">
         <v>-1100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-3200</v>
-      </c>
-      <c r="J21" s="3">
-        <v>4100</v>
       </c>
       <c r="K21" s="3">
         <v>4100</v>
       </c>
       <c r="L21" s="3">
+        <v>4100</v>
+      </c>
+      <c r="M21" s="3">
         <v>8700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3500</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E22" s="3">
         <v>1900</v>
-      </c>
-      <c r="E22" s="3">
-        <v>1800</v>
       </c>
       <c r="F22" s="3">
         <v>1800</v>
       </c>
       <c r="G22" s="3">
+        <v>1800</v>
+      </c>
+      <c r="H22" s="3">
         <v>1900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1600</v>
-      </c>
-      <c r="J22" s="3">
-        <v>1400</v>
       </c>
       <c r="K22" s="3">
         <v>1400</v>
       </c>
       <c r="L22" s="3">
+        <v>1400</v>
+      </c>
+      <c r="M22" s="3">
         <v>900</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
       <c r="N22" s="3">
         <v>0</v>
       </c>
@@ -1307,78 +1346,84 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-3400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-22100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-22300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-13400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>5600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E24" s="3">
+      <c r="D24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24" s="3">
         <v>-300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>300</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -1386,8 +1431,8 @@
       <c r="M24" s="3">
         <v>0</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>4</v>
+      <c r="N24" s="3">
+        <v>0</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>4</v>
@@ -1395,8 +1440,11 @@
       <c r="P24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1439,96 +1487,105 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-3100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-25000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-22400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-13700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>5600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-9200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-5100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-4000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1500</v>
       </c>
-      <c r="K27" s="3">
-        <v>0</v>
-      </c>
       <c r="L27" s="3">
         <v>0</v>
       </c>
       <c r="M27" s="3">
+        <v>0</v>
+      </c>
+      <c r="N27" s="3">
         <v>1900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1571,8 +1628,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1615,8 +1675,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1659,8 +1722,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1703,96 +1769,105 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>4300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1900</v>
       </c>
-      <c r="G32" s="3">
-        <v>-5800</v>
-      </c>
       <c r="H32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I32" s="3">
         <v>-3300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-5000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-3800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-3700</v>
       </c>
     </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-7800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-3800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1500</v>
       </c>
-      <c r="K33" s="3">
-        <v>0</v>
-      </c>
       <c r="L33" s="3">
         <v>0</v>
       </c>
       <c r="M33" s="3">
+        <v>0</v>
+      </c>
+      <c r="N33" s="3">
         <v>1900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1835,101 +1910,110 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-7800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-3800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1500</v>
       </c>
-      <c r="K35" s="3">
-        <v>0</v>
-      </c>
       <c r="L35" s="3">
         <v>0</v>
       </c>
       <c r="M35" s="3">
+        <v>0</v>
+      </c>
+      <c r="N35" s="3">
         <v>1900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1946,8 +2030,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1964,84 +2049,88 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>62800</v>
+      </c>
+      <c r="E41" s="3">
         <v>19400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>33800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>74900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>28500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>51700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>72700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>23800</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M41" s="3">
+      <c r="M41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N41" s="3">
         <v>300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>9800</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>21400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>30100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>35400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>26000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>10000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>9900</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
+      <c r="M42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N42" s="3">
         <v>0</v>
@@ -2052,40 +2141,43 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>189600</v>
+      </c>
+      <c r="E43" s="3">
         <v>193100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>188500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>169600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>165000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>179400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>179600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>179400</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -2096,40 +2188,43 @@
       <c r="P43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>60700</v>
+      </c>
+      <c r="E44" s="3">
         <v>49300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>54300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>44300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>44600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>37800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>41900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>31600</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -2140,8 +2235,11 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2172,11 +2270,11 @@
       <c r="L45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N45" s="3">
         <v>300</v>
-      </c>
-      <c r="N45" s="3">
-        <v>500</v>
       </c>
       <c r="O45" s="3">
         <v>500</v>
@@ -2184,52 +2282,58 @@
       <c r="P45" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>331500</v>
+      </c>
+      <c r="E46" s="3">
         <v>271200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>306300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>324000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>277800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>298400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>307600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>247800</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M46" s="3">
+      <c r="M46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N46" s="3">
         <v>600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2245,8 +2349,8 @@
       <c r="G47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>4</v>
+      <c r="H47" s="3">
+        <v>1800</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>4</v>
@@ -2260,11 +2364,11 @@
       <c r="L47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N47" s="3">
         <v>333900</v>
-      </c>
-      <c r="N47" s="3">
-        <v>333500</v>
       </c>
       <c r="O47" s="3">
         <v>333500</v>
@@ -2272,40 +2376,43 @@
       <c r="P47" s="3">
         <v>333500</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>333500</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>98500</v>
+      </c>
+      <c r="E48" s="3">
         <v>91000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>93100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>84400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>83800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>82400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>79100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>77400</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M48" s="3">
-        <v>0</v>
+      <c r="M48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N48" s="3">
         <v>0</v>
@@ -2316,8 +2423,11 @@
       <c r="P48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2328,7 +2438,7 @@
         <v>13400</v>
       </c>
       <c r="F49" s="3">
-        <v>1200</v>
+        <v>13400</v>
       </c>
       <c r="G49" s="3">
         <v>1200</v>
@@ -2342,14 +2452,14 @@
       <c r="J49" s="3">
         <v>1200</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>4</v>
+      <c r="K49" s="3">
+        <v>1200</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
+      <c r="M49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N49" s="3">
         <v>0</v>
@@ -2360,8 +2470,11 @@
       <c r="P49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2404,8 +2517,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2448,52 +2564,58 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>25600</v>
+      </c>
+      <c r="E52" s="3">
         <v>18800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>18000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>12200</v>
       </c>
-      <c r="G52" s="3">
-        <v>7600</v>
-      </c>
       <c r="H52" s="3">
+        <v>5800</v>
+      </c>
+      <c r="I52" s="3">
         <v>7100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>8300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>7100</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
+      <c r="M52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N52" s="3">
         <v>0</v>
       </c>
       <c r="O52" s="3">
+        <v>0</v>
+      </c>
+      <c r="P52" s="3">
         <v>100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2536,52 +2658,58 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>470300</v>
+      </c>
+      <c r="E54" s="3">
         <v>394800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>430800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>421900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>374500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>394000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>398000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>336200</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M54" s="3">
+      <c r="M54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N54" s="3">
         <v>334500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>334600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>334900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>335100</v>
       </c>
     </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2598,8 +2726,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2616,79 +2745,83 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>170700</v>
+      </c>
+      <c r="E57" s="3">
         <v>155500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>189500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>188300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>127600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>120400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>122200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>111800</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M57" s="3">
+      <c r="M57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N57" s="3">
         <v>900</v>
-      </c>
-      <c r="N57" s="3">
-        <v>1000</v>
       </c>
       <c r="O57" s="3">
         <v>1000</v>
       </c>
       <c r="P57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Q57" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E58" s="3">
         <v>12400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>12500</v>
-      </c>
-      <c r="F58" s="3">
-        <v>7900</v>
       </c>
       <c r="G58" s="3">
         <v>7900</v>
       </c>
       <c r="H58" s="3">
+        <v>7900</v>
+      </c>
+      <c r="I58" s="3">
         <v>7800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>7700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>7500</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L58" s="3" t="s">
         <v>4</v>
       </c>
@@ -2704,35 +2837,38 @@
       <c r="P58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E59" s="3">
         <v>11100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>12100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>18800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>16000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>15700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>19600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>14800</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>4</v>
       </c>
@@ -2748,79 +2884,85 @@
       <c r="P59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>216800</v>
+      </c>
+      <c r="E60" s="3">
         <v>199900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>231600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>233800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>169000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>167900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>162300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>146600</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M60" s="3">
+      <c r="M60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N60" s="3">
         <v>900</v>
-      </c>
-      <c r="N60" s="3">
-        <v>1000</v>
       </c>
       <c r="O60" s="3">
         <v>1000</v>
       </c>
       <c r="P60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Q60" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>138500</v>
+      </c>
+      <c r="E61" s="3">
         <v>135000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>138400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>124900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>125000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>124800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>122000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>123000</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -2836,52 +2978,58 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E62" s="3">
         <v>5900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>6900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>7100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>9700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>8200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>6000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>6100</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N62" s="3">
         <v>15700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>17500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>21200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>21600</v>
       </c>
     </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2924,8 +3072,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2968,8 +3119,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3012,52 +3166,58 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>362300</v>
+      </c>
+      <c r="E66" s="3">
         <v>340700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>376900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>365800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>303700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>300900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>290300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>275600</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M66" s="3">
+      <c r="M66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N66" s="3">
         <v>16500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>18500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>22300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3074,8 +3234,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3118,8 +3279,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3162,8 +3326,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3183,11 +3350,11 @@
         <v>65000</v>
       </c>
       <c r="I70" s="3">
+        <v>65000</v>
+      </c>
+      <c r="J70" s="3">
         <v>62900</v>
       </c>
-      <c r="J70" s="3">
-        <v>0</v>
-      </c>
       <c r="K70" s="3">
         <v>0</v>
       </c>
@@ -3206,8 +3373,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3250,52 +3420,58 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-102200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-103500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-66700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-175600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-161800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-341400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>5800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>24300</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N72" s="3">
         <v>-15600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-17400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-20900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-20300</v>
       </c>
     </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3338,8 +3514,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3382,8 +3561,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3426,52 +3608,58 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-46200</v>
+      </c>
+      <c r="E76" s="3">
         <v>-103800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-40000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-167400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-161700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-341300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>44600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>60600</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M76" s="3">
+      <c r="M76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N76" s="3">
         <v>318000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>316100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>312600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>313200</v>
       </c>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3514,101 +3702,110 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-7800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-3800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1500</v>
       </c>
-      <c r="K81" s="3">
-        <v>0</v>
-      </c>
       <c r="L81" s="3">
         <v>0</v>
       </c>
       <c r="M81" s="3">
+        <v>0</v>
+      </c>
+      <c r="N81" s="3">
         <v>1900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3625,41 +3822,42 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E83" s="3">
         <v>3900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>4100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2200</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
       <c r="N83" s="3">
         <v>0</v>
       </c>
@@ -3669,8 +3867,11 @@
       <c r="P83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3713,8 +3914,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3757,8 +3961,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3801,8 +4008,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3845,8 +4055,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3889,52 +4102,58 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-28100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-33900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>45100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-12000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-3900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-8400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>11600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-200</v>
-      </c>
-      <c r="O89" s="3">
-        <v>-100</v>
       </c>
       <c r="P89" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3951,41 +4170,42 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-6500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2300</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
@@ -3995,8 +4215,11 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4039,8 +4262,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4083,40 +4309,43 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-17200</v>
+      </c>
+      <c r="E94" s="3">
         <v>15000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>1500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-10900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-18400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2600</v>
-      </c>
-      <c r="K94" s="3">
-        <v>-900</v>
       </c>
       <c r="L94" s="3">
         <v>-900</v>
       </c>
       <c r="M94" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="N94" s="3">
         <v>0</v>
@@ -4127,8 +4356,11 @@
       <c r="P94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4145,8 +4377,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4171,8 +4404,8 @@
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -4189,8 +4422,11 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4233,8 +4469,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4277,8 +4516,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4321,41 +4563,44 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>48700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-5500</v>
-      </c>
-      <c r="F100" s="3">
-        <v>-300</v>
       </c>
       <c r="G100" s="3">
         <v>-300</v>
       </c>
       <c r="H100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I100" s="3">
         <v>1200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>54500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-100</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
         <v>0</v>
       </c>
@@ -4365,8 +4610,11 @@
       <c r="P100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4391,8 +4639,8 @@
       <c r="J101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -4409,48 +4657,54 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>43400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-14400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-41100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>46400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-23100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-21100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>48900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-3100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-9800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>10600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-100</v>
       </c>
     </row>
